--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0002T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0002T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.00041109419455</v>
+        <v>7.637566802806614</v>
       </c>
       <c r="D2" t="n">
-        <v>46.81827109027575</v>
+        <v>7.60796905216981</v>
       </c>
       <c r="E2" t="n">
-        <v>13.43912978384475</v>
+        <v>2.183858589874772</v>
       </c>
       <c r="F2" t="n">
-        <v>13.322059633437</v>
+        <v>2.164834690433512</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.01820462645826</v>
+        <v>3.577958251799467</v>
       </c>
       <c r="D3" t="n">
-        <v>21.99219498625847</v>
+        <v>3.573731685267001</v>
       </c>
       <c r="E3" t="n">
-        <v>13.43912978384475</v>
+        <v>2.183858589874772</v>
       </c>
       <c r="F3" t="n">
-        <v>13.322059633437</v>
+        <v>2.164834690433512</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.03034383035867</v>
+        <v>4.392430872433284</v>
       </c>
       <c r="D4" t="n">
-        <v>26.80294839506482</v>
+        <v>4.355479114198033</v>
       </c>
       <c r="E4" t="n">
-        <v>13.43912978384475</v>
+        <v>2.183858589874772</v>
       </c>
       <c r="F4" t="n">
-        <v>13.322059633437</v>
+        <v>2.164834690433512</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.226787443615</v>
+        <v>1.661852959587438</v>
       </c>
       <c r="D5" t="n">
-        <v>10.38024368838131</v>
+        <v>1.686789599361964</v>
       </c>
       <c r="E5" t="n">
-        <v>13.43912978384475</v>
+        <v>2.183858589874772</v>
       </c>
       <c r="F5" t="n">
-        <v>13.322059633437</v>
+        <v>2.164834690433512</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.45882467644216</v>
+        <v>2.837059009921851</v>
       </c>
       <c r="D6" t="n">
-        <v>17.61550824168147</v>
+        <v>2.862520089273239</v>
       </c>
       <c r="E6" t="n">
-        <v>13.43912978384475</v>
+        <v>2.183858589874772</v>
       </c>
       <c r="F6" t="n">
-        <v>13.322059633437</v>
+        <v>2.164834690433512</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>8.664445477688268</v>
+        <v>1.407972390124344</v>
       </c>
       <c r="D7" t="n">
-        <v>8.728840863113582</v>
+        <v>1.418436640255957</v>
       </c>
       <c r="E7" t="n">
-        <v>13.43912978384475</v>
+        <v>2.183858589874772</v>
       </c>
       <c r="F7" t="n">
-        <v>13.322059633437</v>
+        <v>2.164834690433512</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>4.092750979085524</v>
+        <v>0.6650720341013977</v>
       </c>
       <c r="D8" t="n">
-        <v>4.210458290007085</v>
+        <v>0.6841994721261514</v>
       </c>
       <c r="E8" t="n">
-        <v>13.43912978384475</v>
+        <v>2.183858589874772</v>
       </c>
       <c r="F8" t="n">
-        <v>13.322059633437</v>
+        <v>2.164834690433512</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
